--- a/artfynd/A 49789-2023 artfynd.xlsx
+++ b/artfynd/A 49789-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 49789-2023 artfynd.xlsx
+++ b/artfynd/A 49789-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75350633</v>
+        <v>75350632</v>
       </c>
       <c r="B2" t="n">
-        <v>93142</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97785</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,34 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2668</v>
+        <v>2606</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trubbfjädermossa</t>
+          <t>Klippfrullania</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Homalia trichomanoides</t>
+          <t>Frullania tamarisci</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Schimp.</t>
+          <t>(L.) Dumort.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Sandsjöbacka naturreservat, Hl</t>
+          <t>Sandsjöbacka naturreservat, Vg</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>321295.0657552716</v>
+        <v>321286</v>
       </c>
       <c r="R2" t="n">
-        <v>6384849.882959438</v>
+        <v>6384898</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -735,12 +730,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Halland</t>
+          <t>Västergötland</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Lindome</t>
+          <t>Kållered</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -748,19 +743,9 @@
           <t>2018-11-28</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2018-11-28</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -789,6 +774,108 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>75350633</v>
+      </c>
+      <c r="B3" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Sandsjöbacka naturreservat, Hl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>321295</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6384850</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Mölndal</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Halland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lindome</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2018-11-28</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2018-11-28</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>JMN0030, Calluna AB på uppdrag av Länsstyrelsen Västra Götaland. Observatör: Erik Edvardsson.</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson, Erik Edvardsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 49789-2023 artfynd.xlsx
+++ b/artfynd/A 49789-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -774,6 +779,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75350632</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,8 +886,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75350633</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>